--- a/tests/fixtures/excel/paste_specials_pasted.xlsx
+++ b/tests/fixtures/excel/paste_specials_pasted.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C001038-5C55-4C2B-86F3-B70F003E9C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF4878E1-BAC2-4C26-8F20-42258C1D7CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="9840" windowHeight="6720" firstSheet="83" activeTab="83" xr2:uid="{AA29AD23-CBDB-43AF-8C04-921609151AAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="9840" windowHeight="6720" firstSheet="83" activeTab="83" xr2:uid="{E7BB52C2-B423-4036-BE01-12CF065FF986}"/>
   </bookViews>
   <sheets>
     <sheet name="Other" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{56603660-9871-4B93-9016-452E858A9309}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{7D47149E-04BB-4147-AF6E-AB2043B467BD}">
       <text>
         <r>
           <rPr>
@@ -147,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{4275F702-7EFC-4B48-94F5-C770FB740D3B}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{775A3D29-FCE8-4DA5-8CC9-2E5C1C5257D3}">
       <text>
         <r>
           <rPr>
@@ -170,7 +170,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{1DE93133-F5DD-4B26-B03F-803A16AC3F80}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{54EA5996-9148-4A6D-BC80-60BF30F36BDD}">
       <text>
         <r>
           <rPr>
@@ -183,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{D6740E9A-E063-4637-8FEA-C4FDD238871B}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{B7F00B3C-3E07-4212-8648-8DA3462F5E53}">
       <text>
         <r>
           <rPr>
@@ -206,7 +206,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{0FEB70D5-0908-4528-9546-FFE4E8BC96E6}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{3B47CE6F-8961-4B9B-ABF5-90509743D534}">
       <text>
         <r>
           <rPr>
@@ -219,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{E7CC214A-92CB-414C-86CB-B6F4C2F8E923}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{BD2001D5-2B37-4B96-9FD0-89233BCD3D96}">
       <text>
         <r>
           <rPr>
@@ -242,7 +242,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{817B3EF5-2A29-4480-BAD9-59CBDC4A8946}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{74A56767-33BD-4E0B-AF89-089140D3BCCD}">
       <text>
         <r>
           <rPr>
@@ -255,7 +255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{2DDA27CD-83A7-4A09-9241-D349FB36195E}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{CB11E3E1-DF8E-420B-B48F-AF62010BB058}">
       <text>
         <r>
           <rPr>
@@ -268,7 +268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{2EE7618C-0BA6-4760-AC07-5899FC30DC62}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{98BD95F9-59CC-4BAC-8A59-1F4C4EFADF30}">
       <text>
         <r>
           <rPr>
@@ -291,7 +291,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{FE7C74FE-3127-4277-B85B-28C2136A13BC}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{483E477B-65EF-4735-885B-D64254C78A43}">
       <text>
         <r>
           <rPr>
@@ -304,7 +304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{1FB64A72-D7A0-4053-A82D-98558EC18D79}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{2358FF0D-E09C-4A9A-BCC9-3F3AB2D5794D}">
       <text>
         <r>
           <rPr>
@@ -327,7 +327,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{258C0502-8BDC-42A2-B7CA-299E7ADE412B}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{4C521E20-FC97-49D3-A807-B8ACC8D0ECD4}">
       <text>
         <r>
           <rPr>
@@ -340,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{0DB8848E-9EA0-4028-8C3A-49D8FC48F373}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{3AE06F43-0F46-44BA-8462-AED4260EA732}">
       <text>
         <r>
           <rPr>
@@ -363,7 +363,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{D9781E5A-ED6C-44F4-8F17-DC3C80E0B5FA}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{03369668-5C77-4737-8AB2-C08711B51592}">
       <text>
         <r>
           <rPr>
@@ -376,7 +376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{9F7E6B3C-7531-4657-82E2-4D2D71D2D531}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{C1715411-6F38-4E63-87B4-C5A9F64E8B32}">
       <text>
         <r>
           <rPr>
@@ -399,7 +399,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{115C1BCB-E64B-4154-B146-0014BA52332F}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{2A4E1760-840F-4F68-9FD2-6A61072EF42F}">
       <text>
         <r>
           <rPr>
@@ -412,7 +412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{93324492-20E0-4102-9BD4-92C0E93DFD94}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{A6E141AC-C253-4A3A-A49E-CB4F53C0C2B4}">
       <text>
         <r>
           <rPr>
@@ -435,7 +435,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B81B730C-35BC-49AB-BC18-4808BCADC7B5}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B62353F2-92DF-4F6D-8E64-2E0A664B8D45}">
       <text>
         <r>
           <rPr>
@@ -448,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{8CF24053-73C6-49BB-B59D-D8BE0AFA51C4}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{A104BB02-E56A-4204-AD70-F13CCB860E1E}">
       <text>
         <r>
           <rPr>
@@ -471,7 +471,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{58503F49-DBDF-4798-A456-1CDB38483266}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{3707559F-C6A1-4607-9557-CDE54E63E761}">
       <text>
         <r>
           <rPr>
@@ -484,7 +484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{0A2ED7D4-08EA-4E22-B954-8E3AA2896F90}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{12CB5BE3-8C0E-4659-B11C-B18AC246CBFC}">
       <text>
         <r>
           <rPr>
@@ -507,7 +507,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{D10D2C81-7469-4308-956C-ECAC027E5D7F}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{4BEFB097-6A5A-46C7-92D0-3012475798AF}">
       <text>
         <r>
           <rPr>
@@ -520,7 +520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{F3AB86FA-B423-4C28-A464-DFD8A5997140}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{A128A7FB-1035-4811-933E-2798A3CAE37F}">
       <text>
         <r>
           <rPr>
@@ -533,7 +533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{9281070E-10E9-49E4-9286-0CD7DEB254E4}">
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{AA5EB59C-8502-4E76-9ABA-E0BA2AAFA0F8}">
       <text>
         <r>
           <rPr>
@@ -546,7 +546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{71870D2D-926E-4C08-9815-5A53EBCC23A7}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{B077CDB4-BDFC-4B88-B333-9DF9E5543EDA}">
       <text>
         <r>
           <rPr>
@@ -559,7 +559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{7DF1B834-A629-4E35-A2FF-0F5B1DEC719A}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{A4AFC97F-643F-41AD-9EE9-2ACDA61C6693}">
       <text>
         <r>
           <rPr>
@@ -582,7 +582,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B41615E2-570E-4176-BE58-021AF4707F73}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{268B8BDB-1B4E-4CFF-AECD-73A410C81CF3}">
       <text>
         <r>
           <rPr>
@@ -595,7 +595,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{4EA99BAC-CF63-4F82-8AB6-90748927DBA8}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{D7579A70-1C94-4A68-90D4-C128192A2EA9}">
       <text>
         <r>
           <rPr>
@@ -618,7 +618,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{B60BA547-38E5-48B1-9733-A360EB876174}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{A0003D1F-7003-4C5F-844B-B31B22A2A1B5}">
       <text>
         <r>
           <rPr>
@@ -631,7 +631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{02BFFEF5-EE04-4B11-9AA8-F6A917F24EAF}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{6060D622-656C-4D5B-9DA9-186664F8CEFF}">
       <text>
         <r>
           <rPr>
@@ -644,7 +644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{4F321E30-9DCC-4FAA-AF57-45AAC18839E8}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{5A515D57-6018-4EB6-9A83-08F4396236BA}">
       <text>
         <r>
           <rPr>
@@ -657,7 +657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{2A4F31DA-98FB-4BAC-8B56-B6AB9DE34187}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{DEC5455C-2FB5-4FBF-9E6B-26F1569546AF}">
       <text>
         <r>
           <rPr>
@@ -680,7 +680,145 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{3F4ECAE5-888D-4B95-BBEE-3AFD07C38B0F}">
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{EBE5044B-5BDE-46A4-808A-DE31F0C4CBB8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>below</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments22.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{F9D0D4A4-BF50-40D6-9C86-B5748869B33E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>below</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments23.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{6EA63573-9B8A-4527-8F2F-E2718DB4FDAD}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>below</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments24.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{0B2E5B61-CEB4-40C9-984A-D4B7C961D293}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>right</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments25.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{0D0F8513-3AD1-4059-9C93-9FAF06485213}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>right</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments26.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{E3101840-2F30-4DC2-93B7-DB4D5685304A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>right</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments27.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{EC12F542-2BBC-46B7-BD8E-2A575AA88020}">
       <text>
         <r>
           <rPr>
@@ -697,13 +835,13 @@
 </comments>
 </file>
 
-<file path=xl/comments22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments28.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{1FEECF99-DB13-4BEE-BFEB-D28BB259742E}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{A5773146-5106-4F6A-9720-8E04FEA4C4A2}">
       <text>
         <r>
           <rPr>
@@ -716,7 +854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{CC4A88F0-5979-4D4D-822B-8A4D0CE6E79A}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{A21E148D-4F74-4EA9-8C6F-23B39E2D30EA}">
       <text>
         <r>
           <rPr>
@@ -739,7 +877,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{227A8BD9-F669-4ED8-8D74-05FFA5320BA6}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B7BD94B2-884C-48DF-B3A8-D834DCC2CBCA}">
       <text>
         <r>
           <rPr>
@@ -752,7 +890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{177E9058-3200-4640-B639-991B69A65F05}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{5D708601-083E-4C70-9F3A-746A2E20FBEE}">
       <text>
         <r>
           <rPr>
@@ -775,7 +913,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{2C26CBE4-2673-4881-AFF0-F7E53819CB1D}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{3097EE19-DC73-4972-9C4A-A66B7DF64C17}">
       <text>
         <r>
           <rPr>
@@ -788,7 +926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FB3F2515-218D-4253-9B6C-16523A120AB4}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FCDE421A-96F0-4D15-B021-F2D8CD8A2FB6}">
       <text>
         <r>
           <rPr>
@@ -811,7 +949,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{B761C650-32F3-4F42-8087-CD1920EFA036}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{EFA377A2-E2E7-4E6D-AEB9-164DEE6691D5}">
       <text>
         <r>
           <rPr>
@@ -824,7 +962,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{9F155501-BC0C-4A92-8278-A07D1279B29D}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{27E6B7A8-B6BD-487E-9A3C-8A979B89D9F1}">
       <text>
         <r>
           <rPr>
@@ -847,7 +985,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C3CC689A-0167-42A8-95D8-8A18D677229A}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{5276FEA5-F7D1-4A61-93FF-F7BA6D652D6E}">
       <text>
         <r>
           <rPr>
@@ -860,7 +998,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{21B13A70-7A9F-4F88-B66D-550725B26C4A}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{6160F706-9B3F-4EB6-9EC7-392BE89A2A4F}">
       <text>
         <r>
           <rPr>
@@ -883,7 +1021,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{EB0E8AD4-8E96-4CB9-894D-BB5FBF28D304}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{5684FF32-136D-4DB0-BA84-6F4799C5F287}">
       <text>
         <r>
           <rPr>
@@ -896,7 +1034,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{BBF83693-22BE-43CC-8F9C-6A84488D23FE}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{40E8A09C-C49E-49D4-9E1F-867B71BBBA32}">
       <text>
         <r>
           <rPr>
@@ -919,7 +1057,20 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{1BEF3714-A9E6-479A-A068-52B4EA68DDBF}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B75069E0-A700-457F-985F-D28C4C76B0E8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>destination note</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{2E044494-A908-4763-AD14-5543A21B3C6B}">
       <text>
         <r>
           <rPr>
@@ -942,7 +1093,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{0F7CB4BB-C0ED-4B7C-B036-9D24527F7A34}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{EB67EC3F-C727-4491-99F2-5068EA32B2A6}">
       <text>
         <r>
           <rPr>
@@ -955,7 +1106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{6ADB1685-C0A1-48CA-B02D-B23180D8C594}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{CE02BF8E-09A0-49DD-B7D5-D98B7FB5902A}">
       <text>
         <r>
           <rPr>
@@ -1208,7 +1359,7 @@
         <xdr:cNvPr id="2" name="Box">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FAAABC3-1BB9-2142-64E9-CCB47E535D07}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10C1A0D5-5C2D-1A0A-F5CA-F079A6E003FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1273,7 +1424,7 @@
         <xdr:cNvPr id="2" name="Box">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4F8A4E1-5434-9377-3F41-2E50A3EA7976}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B44CCC0A-E5FE-4757-C231-69B5DF1EBF65}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1319,11 +1470,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7726700D-E844-4AF2-9970-B622D7763BD4}" name="Vals" displayName="Vals" ref="A1:B4" totalsRowShown="0">
-  <autoFilter ref="A1:B4" xr:uid="{7726700D-E844-4AF2-9970-B622D7763BD4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9E10C4C5-237A-4047-97FD-24C58D55F852}" name="Vals" displayName="Vals" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4" xr:uid="{9E10C4C5-237A-4047-97FD-24C58D55F852}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0FCCE828-17E2-47C8-B93B-297F635C2553}" name="k"/>
-    <tableColumn id="2" xr3:uid="{33DA6838-3D09-4220-BD76-644EF7AC9A6F}" name="n"/>
+    <tableColumn id="1" xr3:uid="{C59854AD-6757-42A1-9AED-BED61AB13908}" name="k"/>
+    <tableColumn id="2" xr3:uid="{8A5EE005-DFA2-4935-9792-98B743ACA2E1}" name="n"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1645,7 +1796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB7BB48-A8BD-4132-AF45-6D8CF2C9BABC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477712C7-FAB2-445A-9309-5183E29C5147}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1709,7 +1860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72ED8F9-F329-4BFE-8E83-8556CC3CAFBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E361FD-A098-4324-BA2D-CFCF6A79720C}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1813,14 +1964,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{A0BB2CE7-8C52-4C42-8818-5A035553E555}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{1AABEBFA-77D8-440B-A9A9-CC49B1EBBADD}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{2F9BCC57-77A5-4CD0-907A-DC68095CFCAE}"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{6A7A7C67-7E99-41EF-9AD4-DCD5E991BB66}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{797BB226-AF93-4758-9B23-568C55599B84}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{1BD62A7C-D7AB-434D-8CA5-9229637343ED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -1828,7 +1979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F0B68F-E77F-4030-B68E-0E0DEFB65480}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D69CB6E-2A6B-4F21-B1C1-C24DDB032E17}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1931,18 +2082,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{1A25B6EA-3CF3-4C61-A802-20F6C8CE8C78}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{FC091737-F182-4F45-B259-3ED308C35078}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{C2687778-D496-4381-BD64-7698043201DF}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{9ABD4C30-F098-4A49-A2C6-A7169C5AF6BE}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{3FC380EC-9AE5-4E42-9237-EBB8704BA1B4}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{45202619-B1A2-46BF-AE43-844ACC633D20}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{AE9AEAC2-0DB9-428C-9D16-5B10B6F90E87}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{6B40BF48-8C5F-428A-902A-A52C03665575}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -1950,7 +2101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC96F400-2322-401A-B4FA-85AC100AF988}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8897985-CAC1-434F-B82C-DD9F2B5E1860}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2051,18 +2202,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{421A98C5-9E58-4C23-8D6A-6A29F8BE729B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{F131A73B-A9F9-4B9F-A5AF-17A2FC0164E0}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{9FBD0EB8-B107-4B8E-B44D-5340B0409C47}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{47373F29-FFC7-4CF2-8DD3-7E8D006287BE}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{214EE508-700C-468B-A8D8-01E6A4A7752D}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{9B02E5D1-29F3-4A00-BA70-99BC5B2545B3}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{E01E94DE-72AE-42E9-87B3-BF691E62818B}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{6B09678B-9673-4A32-A917-D6C7D0ADE7BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -2070,7 +2221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B12338F0-1027-4208-8258-105D66B916F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B00186A-AAD7-4765-91A6-27B8CBBEEA18}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2167,18 +2318,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{D52C7630-262E-44AC-917C-A6660EE02EAC}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{02E329CB-522C-4068-ACF9-3525BED0A13C}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{EB1C459B-2800-464D-BF8F-B842F4C62A27}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{A3E5CAF5-ACFD-4858-BE22-BD0D9C4A01D9}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{26BD2BA0-12E3-4A67-9128-054F379F53F9}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{A5633F8A-8C75-4B95-AE54-14C92FDD81B9}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{04E087D1-9D4D-4358-A427-410ED8985E74}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{3617BE95-8F15-4229-94A3-DAF66CD54514}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -2186,7 +2337,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403C0B65-C2CF-43B4-932A-9C9C5DA1F70C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664EF036-6E2D-4751-ADD3-444B5A20D7DB}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2295,14 +2446,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{90DC4DDE-B8FE-4F5B-9AD1-5C5E356E1BBB}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{F1BCB2C2-4EA6-48EB-8760-ED221862F42D}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{D6F4FD14-06BD-4372-96D3-EBB9544721AC}"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{A32AEB14-5E98-4765-831C-E14713F944F1}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{5431DBE2-6E34-4953-BBAE-71EC4EEEB29A}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{6DCD6D61-6FC8-4E7B-9786-D8BBE51B3442}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -2310,7 +2461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB67082-BEAA-4D28-8305-3BFF8AFE9E25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E6E5B4-DB7F-408E-A8FC-FB65DB2C7F01}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2418,19 +2569,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{383FAA38-E5F1-4498-B8A3-A775C3BFCAC4}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{82A4161B-5174-407E-988B-E54D75D0329D}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{9977884D-CE2E-48DC-98F9-72FD1D37A631}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{D5F197D7-F3FA-466F-A2F6-63589B0CD904}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{19B5546D-A302-4B44-9E2B-7A37AC9E6E6A}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{542A4DC0-B76A-4202-86A0-328E32F4D198}"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://example.com/source" xr:uid="{EBC1D629-3967-4AD0-982E-B43A542CA825}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{6C3E28AC-95E8-404A-93CB-58B8A10D2CFB}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{A1F1352D-16D9-476F-9096-8128E50B1564}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://example.com/source" xr:uid="{40183690-9149-4571-8DDC-977D5D87D227}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId4"/>
@@ -2438,7 +2589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D4BB0F-1E81-434A-93A3-7CEED4F72890}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7E8D7A-60FB-4221-95B1-DE1CB65E4E97}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2553,15 +2704,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:F1" xr:uid="{782D6B32-409F-496C-8786-C686EF957B75}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:F1" xr:uid="{900A9B97-F4CE-4F1E-B20B-8EDC78BA19AA}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{5A3EA0BD-7F7F-4C8F-88F7-022CBB7D18C8}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{7E8B5859-BFFA-454A-A862-9C72C8B00F9A}"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://example.com/source" xr:uid="{09467D5C-E31E-458A-BA41-5A073F78B51A}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{E45F351D-147E-4789-9E68-6057BDB1271A}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{2D0AA3D7-A62F-4591-BEAD-342B868882FA}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://example.com/source" xr:uid="{B7543E70-EC9D-4C22-828A-529E03AD5CDC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId4"/>
@@ -2569,7 +2720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1BA3F79-5A0C-43AD-B3CD-A65898F3A0A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB7C6A-7C15-42EB-AA7B-D67649409A4A}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2670,18 +2821,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{40237C9D-290C-438B-9923-EE034C9D924F}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{8AC354F7-0AAF-4085-8D28-FAFD1AF42393}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{9A00715F-1E76-4FC7-BD67-CACAD538BC3E}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{13354670-B498-4685-804C-FDF33BD50F0B}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{09858104-3712-4419-B96C-345CF2BEAB1D}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{58F66D61-9533-4289-994C-CFAC9A6F5176}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{7BB5A49C-AAA0-4492-BF01-4D21138FFBE0}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{BBC54BEC-B64A-4D64-8E7C-70A6AA8352F0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -2689,7 +2840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F80CDF0-9183-4897-8959-57AD11D40770}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C031BE90-5329-45AC-A266-7B8F206A0F84}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2790,18 +2941,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{02C640C2-29BE-42A4-904D-A834AD8D62C7}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{E7372423-6639-4B6B-BBB5-294EF542FFF2}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{AC7DFF88-31A2-4493-8443-A733F9FEFEB7}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{D88826A7-D4DD-43F9-8609-6D435344ACBE}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{420CCD91-2B46-4035-B920-A231CF636BAA}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{AF6F0B84-204A-49EE-BF8F-B45F9C4FD317}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{6D05CD0C-B903-4363-970A-B589F9B9F032}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{3AE2E772-77D9-4822-AA23-A16C113FCCEA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -2809,7 +2960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62480F5C-AEFE-4E6B-9A9B-E229759A40B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56E3C89-CFEA-417B-BDE5-3CD0EE97DC81}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2910,18 +3061,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{20D08AA9-7957-4040-8804-00FD1FCEA3FE}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{C873FC85-FF80-4D76-BD1D-E04E04B44C2E}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{8C33E7C6-F172-42C6-99CF-5DEE512C01C4}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{2B537EFA-468A-4B3F-BF49-C054CADF43F1}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{EA097F73-DF74-4692-AB6A-266AF05D1B6F}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{8D567845-B01F-4AD0-9316-28D0AB51E5A5}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{6A858A92-C84D-4F1E-A12C-DD888D33A287}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{242D2348-62A5-4961-9C5B-E46FC6DD6DC2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -2929,7 +3080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7947810F-605C-40AC-B737-3D37504821DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2ED132D-5FF2-4C8F-A827-0D9C230A9F8F}">
   <dimension ref="B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2944,7 +3095,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2757A725-3A6A-40E6-A606-06DB176FE534}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0C9018-BE90-454C-8BC6-B1A14AABB183}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3045,18 +3196,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{9E8F3451-36A3-44A5-A97B-3C7BF7AA5C59}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{4564D159-C9AB-47EC-B1FE-01556B149F7F}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{961D8109-FA0A-49FD-AD64-D8E4A6E82E05}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{2CB682DA-B546-418A-8D53-5930EAD94B2F}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{F94EF8DB-417C-4A5C-8C19-92B3BEDA2C1A}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{7EB063E2-5701-4854-9F00-6722921B3C41}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{FE67DAD7-6C20-4147-8A5D-F8E1E6AF94D3}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{44F0F3E2-A37D-44FE-9A75-7136D0CCC501}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -3064,7 +3215,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5AEDEA7-E99B-4EF0-BD33-E370F115E0AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43817E9-1860-425F-B768-E2A8B392F2FB}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3171,14 +3322,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{DDCA70FC-AB6D-4EE4-A6F6-88EA25509ACA}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{7E487879-8F94-4B20-81EE-3A0ABB9C5D4D}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{B2F934E9-E8FB-44C9-8BBA-3F56CD8E8537}"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{740B5FE3-783B-4E58-AB5B-28229D6F9A8B}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{64C2A5B8-2AA0-413B-AC13-628299B8F7E3}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{E19597C0-0A18-46FB-A481-02B8980F3682}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -3186,7 +3337,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402807F1-7114-4B9D-B293-230E4DFCDE51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75A77CE-4F83-4183-86D8-B6CE7E415CFE}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3237,7 +3388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F011AF8-1FB0-41D7-BF28-8FA064BC0497}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{618D57F5-DDAE-4946-A483-8937C08B5459}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3271,7 +3422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8332591C-4EC3-4DED-B5F7-76874DAA2D8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B53670-A8A4-4D85-AFAE-B4C88706AB77}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3295,7 +3446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922E7BD7-6909-40BD-9EF3-9DE2A3E9176C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526586B3-190F-4419-B585-FC23AF74230C}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3320,7 +3471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893B8743-A771-4C50-B87F-944294C1C3C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44BC9B05-90E6-4793-8153-4104ADD554A0}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3347,7 +3498,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A55717C8-D2F1-45AA-A02A-DA055FADD1D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B729D283-F97D-4766-8A58-19AFA7951F04}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3383,7 +3534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947171BA-0808-4DF2-B2F6-53F7B4FBE788}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4176F2-34A3-4261-A6F1-8A72E2FD7CEB}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3443,7 +3594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B487EB51-C3C6-4C11-B290-1CE98801690A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{794A0D62-C317-4F28-85EC-C4381F09CB29}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3506,7 +3657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3A0D87-14BD-437F-AC4B-881EEA10EFF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07195BC8-0F01-48F8-ADD4-13D058E9267C}">
   <dimension ref="B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3521,7 +3672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED73E514-4B6D-4DAC-A81F-C3E426ADBCFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687F0BD9-64A2-44F7-85C9-CEF603DDCAA0}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3561,7 +3712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9614397B-AE81-48B4-B04B-61427A8EA0C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B084E6-1D31-483B-8875-5B4BE179534E}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3591,7 +3742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62558FC3-36C8-46B3-A1BD-B6F24BFA2A43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190BFD49-1C5F-4F29-B494-5C58E9BFE87E}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3621,7 +3772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AFF204D-B39E-416A-AE54-CEE8A89EC4D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7635B69B-F2B1-4695-8D05-29CCC381B112}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3655,7 +3806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D55D2FB-53A1-48C0-B9F0-040FF716B225}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79787DC7-0D1C-4ACA-84A5-1F7CC52A6EDF}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3725,7 +3876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A4C939-6E59-4E8F-AD1F-D2C1745F7F64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78637A2-122D-43DD-BCCA-C93AC0D957B4}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3775,7 +3926,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2 E2" xr:uid="{5479BF87-2D79-4FD1-9326-A5362940FFBD}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2 E2" xr:uid="{5998C029-DCBF-43D9-8C52-7F099EB999CF}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
@@ -3786,7 +3937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A443A224-3F69-4543-A966-8F6251B78A00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843177F6-4BF9-446D-845F-670D4858461C}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3805,15 +3956,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1" display="https://example.com/one" xr:uid="{397F7886-3A16-45C5-8A39-C74C38BB7D6A}"/>
-    <hyperlink ref="E2" r:id="rId2" display="https://example.com/two" xr:uid="{C305F3CD-E704-48A7-A981-25CE22CD7D10}"/>
+    <hyperlink ref="E1" r:id="rId1" display="https://example.com/one" xr:uid="{96475EC6-2C6F-4BD8-BE88-7CD272BD902D}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://example.com/two" xr:uid="{5F3AA524-9B4B-4862-81F7-D00A9B6BD933}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A44565-7D8E-4F29-A8A7-7537E8C7DA6B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583F8E13-A6BC-463A-8F99-6CBB7C7868CD}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3855,7 +4006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B80DC42-D0B9-4AFC-ADC8-E50ACAFDB278}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CA10F4-5CAC-468F-9475-DBDD2770D444}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3879,7 +4030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D75431FB-A1E0-4C7D-AA07-A96BB66ABFCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3DB635D-BA7C-4062-BEA4-93FD9386FF7D}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3936,11 +4087,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 G1" xr:uid="{5EB0A0FE-846B-4922-A652-CF393F5D421E}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 G1" xr:uid="{DEAC5CF4-216D-4F08-8915-67E5629548DA}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G3" xr:uid="{E153A0D8-DA27-4737-B934-476DD14FA327}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G3" xr:uid="{AC52D3C1-03CB-4C93-89BE-48C447AD057F}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
@@ -3950,7 +4101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B311FBE-3572-4643-87B5-3FB93547F0B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56A1D2C-C042-4D4A-8A26-1E1AA55FC1E5}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4054,14 +4205,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{CA0E78C4-C2D9-4129-AC9F-31431646006B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{15C783E6-A3BC-4F4C-B995-5D242A5528CD}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{368AC82E-6182-4C26-8A16-264FEE95CDCF}"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{0D8A8B88-9C0D-40B2-86E8-F10699E63500}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{4E20B299-B957-47E0-B5C4-459343717D65}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://example.com/source" xr:uid="{05655851-A201-43C3-9FF3-B87C07BF49B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -4069,7 +4220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117B07EA-2B4A-4D22-9324-7938D9CE4F7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43C823B1-0AC0-45BE-BE01-F689A7EFD727}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4098,7 +4249,7 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8115D3B-14B8-4909-A4A5-09A911EF7E79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8CB718C-90C0-4DD9-9DB8-6C9357376367}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4130,7 +4281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA75528-FB86-45F4-856F-CAB79052E270}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7431D79-A3CC-4E00-90C9-FCC086B7AE36}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4324,7 +4475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBD2AE2-AB5B-4C5F-A62C-A2BD0249476B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC5888E-F09A-413F-85DE-75DA6F177560}">
   <dimension ref="B3:N16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4518,7 +4669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C8C335-B548-48DB-B564-C212158CF705}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9334CE44-5793-4A8F-8017-D3B6FA31D177}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4640,7 +4791,7 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E639341-AF1C-4358-AC8C-E44A36DEFC0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCF924D-9691-4326-BBF0-C680D2E114BC}">
   <dimension ref="A3:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4748,7 +4899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F380AB17-06F7-4F45-9B48-AAD0C51480A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B59C045B-AC8F-4178-87C1-95182456D0D7}">
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4812,7 +4963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD1E74B-1077-4B24-869B-3A8244010835}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B53D69-B95A-4347-BBD0-31525F8CA00E}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4870,7 +5021,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A3 E1:G1" xr:uid="{0E32F071-1021-4DEF-81E3-7F010DB7DF6B}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A3 E1:G1" xr:uid="{964958CE-1DE0-4DAD-951A-CE498D3832B2}">
       <formula1>A1&gt;$B$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -4879,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5932990B-732B-43BA-BAD1-7EB4A148BC14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81151C49-2358-4878-8BB8-2BDBC4255B88}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4924,7 +5075,7 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972B672B-2831-47AA-9192-89ADE5237B87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC29D6A-86F9-487C-99A4-8876677633AE}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4966,7 +5117,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F84B36-F2FA-4370-82F7-2F895E535A80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02BFC40F-27BD-4BEA-A4EF-304E81A2EAB3}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5067,18 +5218,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{77468498-2ECA-4A73-8B02-AFFA888E7954}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{45C0A870-694D-4F08-AACA-DBDE26CBFA1F}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{902D31AF-FFE4-4F55-B396-826ABA5EB67A}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{B2E7CBF6-611A-4E86-BC72-9B06186A275F}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{8657842A-B92C-4C3D-A932-33D82EDABA08}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{EB7014CC-0244-4B53-B8EA-7AED95A79E25}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{3F0F011C-4AF1-4538-99E6-58965488E194}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{693DD1F3-6C7A-4479-862C-F39AE67CFBBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -5086,7 +5237,7 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF660E0C-360E-42AF-A4A5-EBF893CFD398}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A23FCDE-1DA1-424D-9C26-46848FD1D9FA}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5134,7 +5285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C5761D-CF34-41B0-AFC5-A164B4972FD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D3D2FA-A397-4B36-87DE-C0869965C6F6}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5168,7 +5319,7 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB045667-06FF-498D-A4C7-31CEF5544707}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D35A85-D0DA-466E-A532-AE68A8C45B60}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5195,7 +5346,7 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13AD941C-39DB-4612-AC4A-5DCCBC1DEF30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC60B5AE-892C-4CF6-A4CF-6E37CEEA9AA1}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5281,7 +5432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B8C48F1-DCD8-49E5-86F5-F0306EA077A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D954728-C170-4D88-89F5-BEBA3697B68C}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5367,7 +5518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F95DEA52-9DBC-4F9D-ACE0-7EBBEF6C6B75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59DA24CF-D6CA-4B0C-A3FB-974533FD73B7}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5442,7 +5593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA90BC28-A84D-4533-9484-74312239CD27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9EDA7DB-297D-463D-830F-522072C2DD84}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5518,7 +5669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50510A0C-C492-4714-9474-EFE19074AAEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5D1E90-E89B-4D19-8C81-5DFFA97C319D}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5568,7 +5719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F39E16-CF72-4F97-9CE9-8476F8F153A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD003ADB-8D6B-4293-9EA8-3EA8247458EB}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5674,7 +5825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D17FA1-5337-40AC-B5A8-94EBA4ED83E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A28250D-D98B-4CC7-B089-0702328E936A}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5717,7 +5868,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E3EFC6-B9A7-471B-892D-7FE4D7C4C338}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A634AE9-453E-4995-A6EB-865837F9BD35}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5814,18 +5965,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{CC3C5BDA-4CDD-47E1-BF08-056847A75171}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{DBAEEE43-9881-4954-9558-A77AADF772A7}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{71236F9B-CC52-4DF6-A55D-ED288B521A24}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{95D948B8-34D7-439B-93FA-320C031B481C}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{D82BF0BE-76F2-43AB-939F-55B2BA4B683F}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{33437D4D-6E35-4A5D-B664-DD10E7C7D745}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{CB9B7E93-0B55-47A7-A470-C712AF9A85CF}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{D08B3BC4-7B9E-4807-A262-6189300F6733}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -5833,7 +5984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9EC69D8-BC01-4E08-BFE5-D7A3F96ED930}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364FD136-25F6-4C03-BAE7-1F47F3756691}">
   <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6246,7 +6397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C87CC-7DF9-401A-BB09-3C880EB4384D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47ED689F-A344-4C5C-9FA2-094B50F7C35B}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6346,7 +6497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4997214C-2F38-4C2E-83A1-E6A9B75AA53C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371F9C9B-C1A4-411A-86D8-2A66AD91E9A2}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6403,7 +6554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A17D486-1B1F-4D86-AD01-A62DA73A44DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD636DAD-AAC7-4D5B-82EE-5A485E912E51}">
   <dimension ref="E1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6433,7 +6584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F227CC8-3C90-4F22-8A3B-23C03F6C01EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719304EE-4446-4A83-8002-489680371AD5}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6483,7 +6634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB962E20-6C68-421C-AB38-07C1D3EDE905}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC933313-43AA-4EFE-9523-30B6A88708CA}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6516,7 +6667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB503518-A10A-4FD2-A4CE-440344CCB845}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989CB2E5-5EEA-4E2D-8C42-154C8E8C397B}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6542,7 +6693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA08BEC8-4D3E-45C3-B237-7055DE9396DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF99E659-6BAC-4764-91E8-9FE0FE2BDD26}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6568,65 +6719,69 @@
 </file>
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304BFB4A-AA24-4CD4-892E-1E8EC18B4AB9}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969515FF-1A4E-4459-961E-1A419904F0E4}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
     </row>
-    <row r="6" spans="1:1" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>9</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC4954F-F8BF-4111-A751-C2500C52CCB7}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4638A-2031-4747-8273-98E338711002}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E289D3D9-558F-4484-BCDA-2B5F3FE533E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76FE166A-E036-40DE-9F17-46E486C72FC4}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6729,18 +6884,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{4C57604E-A064-4C8B-A3CE-65D1F3E11807}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{236B5796-D70F-4B7B-9ADF-96E8CF71CF79}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{BB695637-3D36-4041-8CC2-D26C86E44EF1}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{85FF6289-B43D-4368-B638-D16BDC7F6401}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{BB18E09C-D65C-4C6A-AC75-B34B856DD7B4}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{595DD022-D13C-47A0-8A56-82EE8EB4F31F}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{D3714D01-4657-4A42-B12C-77C2E2C3EE38}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{31E1F633-3FD6-4B31-87F4-3E9848E0E362}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -6748,38 +6903,40 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E70652F-D675-4658-83A4-BFF9DE225BBD}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5094758-2820-4555-A253-7D71DB6FF521}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BEC350C-B22D-487E-A012-DAF01B4D2852}">
-  <dimension ref="A1:F1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B68EED82-E207-434B-B61A-02C6653541DA}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6788,7 +6945,7 @@
     <col min="6" max="6" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
@@ -6802,14 +6959,16 @@
         <v>1</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BC9802-6D42-487F-85F7-C35EA5D1D9DB}">
-  <dimension ref="A1:F1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3E0686-500D-40AD-8D3A-4C21BE5DA7C8}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6818,7 +6977,7 @@
     <col min="6" max="6" width="0" style="5" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
@@ -6826,14 +6985,16 @@
         <v>1</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{067C7A8E-33FF-423A-BD61-3013618EEC8F}">
-  <dimension ref="A1:E1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F85772B-84D0-4A2F-9D98-44458F6E5CF4}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6842,7 +7003,7 @@
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
@@ -6850,13 +7011,15 @@
         <v>1</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590DDF6D-759F-4A16-BCFE-42FD2DC8D911}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E39474-8C72-4E0C-97DA-F000F77A0C7F}">
   <dimension ref="B1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6893,7 +7056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EE9DD34-5435-40F0-AB99-73718BDC3517}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82FBD742-0D32-4AFE-B573-FB786252E0B7}">
   <dimension ref="A2:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -6922,7 +7085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE10589E-E4D4-4EE4-A1DF-2F2AAEAED1A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DA8827-69D0-4361-9DE6-FB67AC2F0E87}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6962,7 +7125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{857C52D9-328E-4686-AEF2-A9124FFAC1FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB598761-DB65-4080-A1CB-AB7EC2F7825C}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6992,7 +7155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835C6B22-58A0-4399-95C0-324926715B1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CABDB3B-B76A-4721-83B1-B496CB462C03}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7019,7 +7182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B37F437-8E59-406E-B2C7-8FE1B88E6456}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7996461F-B213-497D-9F52-D9E656DE8E3C}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7041,15 +7204,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1" display="https://example.com/one" xr:uid="{855EC70D-D289-433E-9123-5F371CC18AE8}"/>
-    <hyperlink ref="E2" r:id="rId2" display="https://example.com/two" xr:uid="{36870B7B-1522-4590-B35C-A90E4911E5E4}"/>
+    <hyperlink ref="E1" r:id="rId1" display="https://example.com/one" xr:uid="{D0A5246F-CA4D-4254-85D4-044D78A6AE14}"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://example.com/two" xr:uid="{7E478A14-1594-4B0C-BAFE-9ED81E01115A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463C0292-4F94-45F8-AA61-F9CB82A1B3F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB841FC-5522-4A22-AED7-A91A4A11D25F}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7150,18 +7313,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{1C13A17D-8F70-4ABC-B803-40C7DC28FA57}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2" xr:uid="{4519E037-51E9-4C86-AF5D-C9ECCA020B3B}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{164B4DC8-B12C-46A4-B2B4-3BBABC7EA64B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2" xr:uid="{267CE8D4-A314-460A-8D16-C5010641C6A2}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{DB857531-CF0B-46AD-AB9C-5590F281A27D}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{22864A42-04D8-4F9B-A1F5-E22A7FC4655C}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{C79E6CD2-AF52-4BB9-82AA-6191902BF955}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{82AFD74E-E30D-4F78-B4DC-ABCF07CDE1CA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -7169,7 +7332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF54206-B1BB-4F9B-9305-A6D1EB7B8FEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5B85C79-464C-47F0-B8DA-2E528F5BDDC2}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7213,7 +7376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EE1F8A-BB75-46B1-9CA4-4A5FCB9CED9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B594B1BD-3E61-4B02-A0B0-2DAD286C5F70}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7245,7 +7408,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://example.com/kept" xr:uid="{AE673FFD-D599-4266-BCAD-F8B05E7A64DF}"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://example.com/kept" xr:uid="{806B8A49-84D4-41C7-A7C5-3F772075639E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
@@ -7253,7 +7416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34D790C0-EB3D-4F89-9309-D9336660C327}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C0A480D-6479-4688-9FB3-F23680112D8F}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7305,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F0B01D3-8748-4460-AA5E-646ADDDB1963}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A9C4F9-D270-4A7D-B8A8-B7FD3F3FFC89}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7349,7 +7512,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A6" xr:uid="{3F0B01D3-8748-4460-AA5E-646ADDDB1963}">
+  <autoFilter ref="A1:A6" xr:uid="{C9A9C4F9-D270-4A7D-B8A8-B7FD3F3FFC89}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="greaterThan" val="2"/>
@@ -7361,7 +7524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563DF1E7-21E2-4A66-9917-BFA58AEFCD7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD6CC65-2055-4CB7-8341-EF5990AF2F88}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7387,7 +7550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB6A617-C750-4C31-8D4A-67265B734BBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F737747-D67B-49D4-95BC-9D4CEC435AF6}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7435,7 +7598,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A6" xr:uid="{5EB6A617-C750-4C31-8D4A-67265B734BBE}">
+  <autoFilter ref="A1:A6" xr:uid="{4F737747-D67B-49D4-95BC-9D4CEC435AF6}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="greaterThan" val="2"/>
@@ -7447,7 +7610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D62ACF8-19EA-4920-AECC-348D608BED96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8970E85-31D4-47FE-9A84-CB8843D161C7}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7483,7 +7646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6155031-2F3D-4A08-93B2-012FFB6ED74C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F25687-713C-4522-894A-CAC3BBB9EDD1}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7564,7 +7727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3549D62A-5354-4755-AA51-EC1AEC81E321}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2173AD0E-42BD-40D4-B7ED-F5CD950E715F}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7617,7 +7780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1D1619-D6C5-4027-9205-C4E245822A4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95F7365-7DC4-4713-B1A4-792261385CD9}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7653,7 +7816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC5963F-3E52-4AD7-991E-AF9ADB11602E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE85FFF-BB5E-4270-B2D1-BE6195E065F1}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7754,14 +7917,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{BE679CE3-C83F-499B-9949-6B7DBF1E4777}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A2 E1:E2" xr:uid="{D45278E5-7E87-4E9F-B0E7-06E31A1CFDB9}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{81DC006D-6369-4AFB-90F8-5CEF78890266}"/>
-    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{F5EDC269-DAC9-4DBE-9E39-E27AB328DB9A}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://example.com/source" xr:uid="{49044B71-7764-4C75-B0D7-9DFA793FC533}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://example.com/destination" xr:uid="{93EE3FA7-5389-4533-9937-F243B86614BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
@@ -7769,7 +7932,7 @@
 </file>
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E433606-E4B6-4DFD-8B98-7C777F278B0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D5DCFA-6801-4A3E-8D1E-21724034A0AD}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7788,7 +7951,7 @@
 </file>
 
 <file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04317F3B-49A9-4827-8EA0-20D842FB2687}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD736545-65E9-4026-9F2F-ACF3A30FB426}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
